--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -617,7 +617,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>93</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-socialhistory.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-socialhistory.xlsx
@@ -645,6 +645,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="social-history"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -799,9 +807,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>social-history</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1299,7 +1304,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -3840,7 +3845,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3859,7 +3864,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3912,10 +3917,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3938,13 +3943,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3995,7 +4000,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4019,7 +4024,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4030,10 +4035,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4062,7 +4067,7 @@
         <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>142</v>
@@ -4103,10 +4108,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4115,7 +4120,7 @@
         <v>194</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4139,7 +4144,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4150,10 +4155,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4176,19 +4181,19 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4237,7 +4242,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4258,10 +4263,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4272,10 +4277,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4298,13 +4303,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4355,7 +4360,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4379,7 +4384,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4390,10 +4395,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4422,7 +4427,7 @@
         <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>142</v>
@@ -4463,10 +4468,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4475,7 +4480,7 @@
         <v>194</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4499,7 +4504,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4510,10 +4515,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4539,23 +4544,23 @@
         <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4597,7 +4602,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4618,10 +4623,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4632,10 +4637,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4658,16 +4663,16 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4717,7 +4722,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4738,10 +4743,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4752,10 +4757,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4781,21 +4786,21 @@
         <v>113</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4898,7 +4903,7 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>259</v>
@@ -5140,7 +5145,7 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>277</v>
@@ -7202,13 +7207,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7259,7 +7264,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7283,7 +7288,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7326,7 +7331,7 @@
         <v>140</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>142</v>
@@ -7379,7 +7384,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7403,7 +7408,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -8162,7 +8167,7 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>466</v>
@@ -8642,13 +8647,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8699,7 +8704,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8723,7 +8728,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8766,7 +8771,7 @@
         <v>140</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>142</v>
@@ -8819,7 +8824,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8843,7 +8848,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
